--- a/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVictimas.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8178B7E-3196-4353-A00F-B3A5CFFAD061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242CC9AA-041F-4E97-9788-3E944235B490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6528" yWindow="2148" windowWidth="17280" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="anual" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">anual!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">anual!$A$1:$J$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="10">
   <si>
     <t>Año</t>
   </si>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -483,346 +483,348 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
       <c r="C9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>77</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>88</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>137</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>2095</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>2614</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>3073</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>1797</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24">
-        <v>2077</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>1790</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>791</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>989</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>1053</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>872</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30">
-        <v>1425</v>
+        <v>791</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
       </c>
       <c r="C31">
-        <v>1655</v>
+        <v>989</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>872</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -830,10 +832,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -841,10 +843,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -852,39 +854,113 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
